--- a/data/percent_changes.xlsx
+++ b/data/percent_changes.xlsx
@@ -477,25 +477,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.19</v>
+        <v>1.187437657689383</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.02</v>
+        <v>-0.01805666363223768</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>-0.004094685696065525</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.44</v>
+        <v>-1.439315201270586</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.24</v>
+        <v>-0.2446863223154128</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.45</v>
+        <v>-1.431801055011273</v>
       </c>
       <c r="H2" t="n">
-        <v>3.55</v>
+        <v>3.546698086459044</v>
       </c>
     </row>
     <row r="3">
@@ -505,25 +505,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.18</v>
+        <v>1.17772024515137</v>
       </c>
       <c r="C3" t="n">
-        <v>0.38</v>
+        <v>0.3801986835304083</v>
       </c>
       <c r="D3" t="n">
-        <v>0.38</v>
+        <v>0.3804156422562155</v>
       </c>
       <c r="E3" t="n">
-        <v>1.72</v>
+        <v>1.716203487028789</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.03</v>
+        <v>-2.028060622590067</v>
       </c>
       <c r="G3" t="n">
-        <v>1.65</v>
+        <v>1.663886572143491</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.13</v>
+        <v>-0.1299412526137744</v>
       </c>
     </row>
     <row r="4">
@@ -533,25 +533,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.96</v>
+        <v>2.962116107701873</v>
       </c>
       <c r="C4" t="n">
-        <v>3.09</v>
+        <v>3.093444767194953</v>
       </c>
       <c r="D4" t="n">
-        <v>2.71</v>
+        <v>2.70922008866199</v>
       </c>
       <c r="E4" t="n">
-        <v>5.27</v>
+        <v>5.269086438132042</v>
       </c>
       <c r="F4" t="n">
-        <v>4.27</v>
+        <v>4.264948307924255</v>
       </c>
       <c r="G4" t="n">
-        <v>5.23</v>
+        <v>5.178735015889857</v>
       </c>
       <c r="H4" t="n">
-        <v>2.69</v>
+        <v>2.69764278208986</v>
       </c>
     </row>
     <row r="5">
@@ -561,25 +561,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.38</v>
+        <v>-1.375236996095841</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.84</v>
+        <v>-1.835917830393374</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.56</v>
+        <v>-2.563211392371589</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.76</v>
+        <v>-0.7551706700099636</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.84</v>
+        <v>-1.841159016683025</v>
       </c>
       <c r="G5" t="n">
-        <v>0.26</v>
+        <v>0.3138510451797361</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.16</v>
+        <v>-3.178371754614362</v>
       </c>
     </row>
     <row r="6">
@@ -589,25 +589,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-3.35</v>
+        <v>-3.345653244592195</v>
       </c>
       <c r="C6" t="n">
-        <v>-2.52</v>
+        <v>-2.517390672760977</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.77</v>
+        <v>-2.770938634659859</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.73</v>
+        <v>-4.725444973873238</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.56</v>
+        <v>-2.556370154274967</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.76</v>
+        <v>-3.778866340097953</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.04</v>
+        <v>-4.043418874264404</v>
       </c>
     </row>
     <row r="7">
@@ -617,25 +617,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.47</v>
+        <v>0.4706529552406469</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.54</v>
+        <v>-1.536574964986848</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.55</v>
+        <v>-0.5457980949675756</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.35</v>
+        <v>-2.351565029669977</v>
       </c>
       <c r="F7" t="n">
-        <v>0.42</v>
+        <v>0.4173617482692737</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.89</v>
+        <v>-4.856140350877158</v>
       </c>
       <c r="H7" t="n">
-        <v>0.78</v>
+        <v>0.7933824522864397</v>
       </c>
     </row>
     <row r="8">
@@ -645,25 +645,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.62</v>
+        <v>1.616515706635369</v>
       </c>
       <c r="C8" t="n">
-        <v>0.76</v>
+        <v>0.7622798936480768</v>
       </c>
       <c r="D8" t="n">
-        <v>1.13</v>
+        <v>1.133445145749379</v>
       </c>
       <c r="E8" t="n">
-        <v>0.72</v>
+        <v>0.7213495280033344</v>
       </c>
       <c r="F8" t="n">
-        <v>0.18</v>
+        <v>0.1790997009959217</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.21</v>
+        <v>-1.223475349452696</v>
       </c>
       <c r="H8" t="n">
-        <v>2.42</v>
+        <v>2.425889051288199</v>
       </c>
     </row>
     <row r="9">
@@ -673,25 +673,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1.88</v>
+        <v>-1.88286830320874</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.86</v>
+        <v>-0.8618939173844042</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.38</v>
+        <v>-0.3805572798652568</v>
       </c>
       <c r="E9" t="n">
-        <v>0.21</v>
+        <v>0.2080015870816521</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.59</v>
+        <v>-1.590268982732379</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.19</v>
+        <v>-0.2464889653195246</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.27</v>
+        <v>-1.281289994624257</v>
       </c>
     </row>
     <row r="10">
@@ -701,25 +701,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-2.49</v>
+        <v>-2.489694799517006</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.46</v>
+        <v>-0.464911556765979</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.5616054789677638</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.16</v>
+        <v>-1.164372988826512</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.77</v>
+        <v>-0.7720392277424382</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.03</v>
+        <v>-2.998013364637919</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.66</v>
+        <v>-1.647890324440171</v>
       </c>
     </row>
     <row r="11">
@@ -729,25 +729,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-1.16</v>
+        <v>-1.163689389620848</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.11</v>
+        <v>-0.1075672986567966</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.24</v>
+        <v>-0.2413990364840579</v>
       </c>
       <c r="E11" t="n">
-        <v>1.2</v>
+        <v>1.196111316683557</v>
       </c>
       <c r="F11" t="n">
-        <v>0.57</v>
+        <v>0.5703348861255009</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.49</v>
+        <v>-0.5166635635821648</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.45</v>
+        <v>-1.452525355486456</v>
       </c>
     </row>
     <row r="12">
@@ -757,25 +757,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-1.26</v>
+        <v>-1.259778735684935</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.53</v>
+        <v>-0.5289089917073997</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.47</v>
+        <v>-0.465706253459619</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.31</v>
+        <v>-1.309448903029731</v>
       </c>
       <c r="F12" t="n">
-        <v>0.43</v>
+        <v>0.4287159575631749</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.26</v>
+        <v>-2.226641089224746</v>
       </c>
       <c r="H12" t="n">
-        <v>0.14</v>
+        <v>0.1222460695076588</v>
       </c>
     </row>
     <row r="13">
@@ -785,25 +785,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.2</v>
+        <v>3.203991436420939</v>
       </c>
       <c r="C13" t="n">
-        <v>1.04</v>
+        <v>1.039644173623477</v>
       </c>
       <c r="D13" t="n">
-        <v>2.15</v>
+        <v>2.154856501215363</v>
       </c>
       <c r="E13" t="n">
-        <v>1.36</v>
+        <v>1.356607995823378</v>
       </c>
       <c r="F13" t="n">
-        <v>1.49</v>
+        <v>1.486635778998813</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3</v>
+        <v>-0.3249254681271463</v>
       </c>
       <c r="H13" t="n">
-        <v>2.52</v>
+        <v>2.536010811152822</v>
       </c>
     </row>
   </sheetData>
